--- a/artfynd/A 6612-2026 artfynd.xlsx
+++ b/artfynd/A 6612-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121639312</v>
+        <v>121639311</v>
       </c>
       <c r="B2" t="n">
-        <v>57518</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590296</v>
+        <v>590314</v>
       </c>
       <c r="R2" t="n">
-        <v>6762845</v>
+        <v>6762879</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -753,6 +748,11 @@
           <t>2024-05-23</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,6 +774,840 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>JMN0138 NVI Ockelbo-Grönviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120970066</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>N om Ockelbo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>590102</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6762935</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-05-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega, Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121639317</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ockelbo-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>590317</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6762837</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>JMN0138 NVI Ockelbo-Grönviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121639312</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ockelbo-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>590296</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6762845</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>JMN0138 NVI Ockelbo-Grönviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121639306</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ockelbo-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>590269</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6762912</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>JMN0138 NVI Ockelbo-Grönviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121639307</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ockelbo-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>590287</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6762898</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>stort bestånd</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>JMN0138 NVI Ockelbo-Grönviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121639309</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ockelbo-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>590316</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6762879</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>rikligt bestånd på plats. Minst 30 plantor.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>JMN0138 NVI Ockelbo-Grönviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121639315</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ockelbo-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>590323</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6762834</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>JMN0138 NVI Ockelbo-Grönviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121639346</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ockelbo-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>590283</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6762895</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>JMN0138 NVI Ockelbo-Grönviken</t>
         </is>
